--- a/reports/signals_2026-10-19.xlsx
+++ b/reports/signals_2026-10-19.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'سیگنال‌ها'!$A$1:$P$714</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'تصمیم‌های ۱۰ دقیقه‌ای'!$A$1:$K$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'دقت روزهای قبل'!$A$1:$L$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'تصمیم‌های ۱۰ دقیقه‌ای'!$A$1:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'دقت روزهای قبل'!$A$1:$L$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'کالیبراسیون'!$A$1:$E$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'راهنما'!$A$1:$B$14</definedName>
   </definedNames>
@@ -43881,7 +43881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -43957,57 +43957,57 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>قیستو</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>R3-برگشت</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>46330</v>
+        <v>3010</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>2.886964246058188</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G2" s="13" t="n">
-        <v>0.3032883801844323</v>
+        <v>3</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>-0.2449319272511801</v>
+        <v>0</v>
       </c>
       <c r="I2" s="13" t="n">
-        <v>4.585131320735435</v>
+        <v>0.3112682698461984</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>-0.2449319272511801</v>
+        <v>0</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>دکیمی</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -44021,38 +44021,38 @@
         </is>
       </c>
       <c r="E3" s="12" t="n">
-        <v>3000</v>
+        <v>80570</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>2.389078498293506</v>
+        <v>2.97801635991819</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>2.883779499650276</v>
+        <v>3.667120777939588</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0.0144512562411362</v>
+        <v>0.6688721785247623</v>
       </c>
       <c r="I3" s="13" t="n">
-        <v>0.6016481570125709</v>
+        <v>3.749389333597513</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>0.0144512562411362</v>
+        <v>0.6688721785247623</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>دکیمی</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -44066,88 +44066,88 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>80560</v>
+        <v>7810</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>2.965235173824121</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>1.511603679674598</v>
+        <v>1.617630737075154</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.4780144794683699</v>
+        <v>-0.119756791065459</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>2.76081034562369</v>
+        <v>4.262783200150274</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>0.4780144794683699</v>
+        <v>-0.119756791065459</v>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فنر</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>R3-برگشت</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>7780</v>
+        <v>7600</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>2.503293807641627</v>
+        <v>1.87667560321716</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1.971412624499198</v>
+        <v>1.344827586206897</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.0797488641245581</v>
+        <v>0</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>3.025566232158573</v>
+        <v>4.281704922600333</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>0.0797488641245581</v>
+        <v>0</v>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>وثخوز</t>
+          <t>موج</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>صندوق-اهرمی</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -44156,22 +44156,22 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>5120</v>
+        <v>105857</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>2.811244979919669</v>
+        <v>3.999567720511665</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2.2</v>
+        <v>2.090651450754753</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0</v>
+        <v>0.089570795403815</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>2.543129007060554</v>
+        <v>3.151622756565823</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>0</v>
+        <v>0.089570795403815</v>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
@@ -44187,36 +44187,36 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>قیستو</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>R3-برگشت</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>17970</v>
+        <v>46330</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>2.886964246058188</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1.747260057365575</v>
+        <v>0.3032883801844323</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.3503341815947931</v>
+        <v>-0.2449319272511801</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>0.8945515503438495</v>
+        <v>4.585131320735435</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.3503341815947931</v>
+        <v>-0.2449319272511801</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -44246,22 +44246,22 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>14220</v>
+        <v>3000</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2.968863142650258</v>
+        <v>2.389078498293506</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1.5</v>
+        <v>2.883779499650276</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0</v>
+        <v>0.0144512562411362</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.5578484611619859</v>
+        <v>0.6016481570125709</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0</v>
+        <v>0.0144512562411362</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
@@ -44272,12 +44272,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>دکیمی</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -44291,38 +44291,38 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>14220</v>
+        <v>80560</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>2.968863142650258</v>
+        <v>2.965235173824121</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1.8</v>
+        <v>1.511603679674598</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0</v>
+        <v>0.4780144794683699</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0.4102634114447916</v>
+        <v>2.76081034562369</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0</v>
+        <v>0.4780144794683699</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -44336,78 +44336,78 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3010</v>
+        <v>7780</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>2.503293807641627</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>2.511887478745728</v>
+        <v>1.971412624499198</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.0047324885554444</v>
+        <v>0.0797488641245581</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1.226384466052744</v>
+        <v>3.025566232158573</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.0047324885554444</v>
+        <v>0.0797488641245581</v>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>وثخوز</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>7780</v>
+        <v>5120</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>2.503293807641627</v>
+        <v>2.811244979919669</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1.937953146007207</v>
+        <v>2.2</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.0748510230485067</v>
+        <v>0</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>2.148671686449225</v>
+        <v>2.543129007060554</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.0748510230485067</v>
+        <v>0</v>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -44426,33 +44426,33 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>17960</v>
+        <v>17970</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>2.922636103151865</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1.802517007736404</v>
+        <v>1.747260057365575</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.3791563499194397</v>
+        <v>0.3503341815947931</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.9656167208363858</v>
+        <v>0.8945515503438495</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.3791563499194397</v>
+        <v>0.3503341815947931</v>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -44477,32 +44477,32 @@
         <v>2.968863142650258</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>2.294588075537954</v>
+        <v>1.5</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.101853692475897</v>
+        <v>0</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>4.296725462309438</v>
+        <v>0.5578484611619859</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0.1035928141721343</v>
+        <v>0</v>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -44516,38 +44516,38 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3010</v>
+        <v>14220</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>2.968863142650258</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>2.609743601885966</v>
+        <v>1.8</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.0037335475710812</v>
+        <v>0</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>1.166117520504931</v>
+        <v>0.4102634114447916</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.0040169860079247</v>
+        <v>0</v>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -44561,38 +44561,38 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>7770</v>
+        <v>3010</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>2.371541501976293</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>2.057145991993271</v>
+        <v>2.511887478745728</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.1073792672259145</v>
+        <v>0.0047324885554444</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>1.629143157649846</v>
+        <v>1.226384466052744</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>0.6051925671343392</v>
+        <v>0.0047324885554444</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -44606,22 +44606,22 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>17970</v>
+        <v>7780</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>2.503293807641627</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1.763826404181855</v>
+        <v>1.937953146007207</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.4550311625049397</v>
+        <v>0.0748510230485067</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.9601568893539276</v>
+        <v>2.148671686449225</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.5031200868174435</v>
+        <v>0.0748510230485067</v>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
@@ -44632,97 +44632,97 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>4420</v>
+        <v>17960</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>-2.428256070640178</v>
+        <v>2.922636103151865</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.5592951260779933</v>
+        <v>1.802517007736404</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-0.0695371180306478</v>
+        <v>0.3791563499194397</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>4.556722691614141</v>
+        <v>0.9656167208363858</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>-0.0832377058982619</v>
+        <v>0.3791563499194397</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>5730</v>
+        <v>14220</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.968863142650258</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.5956069975800256</v>
+        <v>2.294588075537954</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>-0.146157533717874</v>
+        <v>0.101853692475897</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>1.842626321390354</v>
+        <v>4.296725462309438</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>-0.2510075565171826</v>
+        <v>0.1035928141721343</v>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -44747,16 +44747,16 @@
         <v>2.730375426621157</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>3.121360733168777</v>
+        <v>2.609743601885966</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.0032837031454741</v>
+        <v>0.0037335475710812</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>1.060789152121727</v>
+        <v>1.166117520504931</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>0</v>
+        <v>0.0040169860079247</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -44786,33 +44786,33 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>7790</v>
+        <v>7770</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>2.635046113306982</v>
+        <v>2.371541501976293</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>2.198364318980956</v>
+        <v>2.057145991993271</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.0567645318085804</v>
+        <v>0.1073792672259145</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>1.440235725763299</v>
+        <v>1.629143157649846</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>-0.0638996971329605</v>
+        <v>0.6051925671343392</v>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -44831,22 +44831,22 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>17860</v>
+        <v>17970</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>2.34957020057307</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1.679640206724881</v>
+        <v>1.763826404181855</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.425716299276451</v>
+        <v>0.4550311625049397</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0.8208899988227195</v>
+        <v>0.9601568893539276</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>0.4839560455987503</v>
+        <v>0.5031200868174435</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -44857,52 +44857,52 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>14220</v>
+        <v>4420</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>2.968863142650258</v>
+        <v>-2.428256070640178</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>2.538077872452422</v>
+        <v>0.5592951260779933</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.1034251141854599</v>
+        <v>-0.0695371180306478</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>3.499474508348878</v>
+        <v>4.556722691614141</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.110470391337025</v>
+        <v>-0.0832377058982619</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -44927,32 +44927,32 @@
         <v>-2.881355932203389</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.5730171617519209</v>
+        <v>0.5956069975800256</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>-0.1417664892174653</v>
+        <v>-0.146157533717874</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>1.581700301737103</v>
+        <v>1.842626321390354</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>-0.4608943704454772</v>
+        <v>-0.2510075565171826</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -44966,128 +44966,128 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>17900</v>
+        <v>3010</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>2.57879656160458</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>1.729232534027776</v>
+        <v>3.121360733168777</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.3985229729363614</v>
+        <v>0.0032837031454741</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0.7303133776464583</v>
+        <v>1.060789152121727</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.4362136763476879</v>
+        <v>0</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>4430</v>
+        <v>7790</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-2.207505518763797</v>
+        <v>2.635046113306982</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.5976561705729136</v>
+        <v>2.198364318980956</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>-0.0535687346682349</v>
+        <v>0.0567645318085804</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>4.347888187658796</v>
+        <v>1.440235725763299</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>-0.0320687419588898</v>
+        <v>-0.0638996971329605</v>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>5730</v>
+        <v>17860</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.34957020057307</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.5540285769783065</v>
+        <v>1.679640206724881</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>-0.140322221631417</v>
+        <v>0.425716299276451</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>1.369303324163979</v>
+        <v>0.8208899988227195</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>-0.5994527842663226</v>
+        <v>0.4839560455987503</v>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -45101,78 +45101,78 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>3000</v>
+        <v>14220</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>2.389078498293506</v>
+        <v>2.968863142650258</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>2.907277713201065</v>
+        <v>2.538077872452422</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.0025032741688276</v>
+        <v>0.1034251141854599</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>0.9939061925160714</v>
+        <v>3.499474508348878</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>0</v>
+        <v>0.110470391337025</v>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>7810</v>
+        <v>5730</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1.794061189744712</v>
+        <v>0.5730171617519209</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>-0.009767218856966599</v>
+        <v>-0.1417664892174653</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>1.185695830206121</v>
+        <v>1.581700301737103</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>-0.4363419826010773</v>
+        <v>-0.4608943704454772</v>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -45191,22 +45191,22 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>17970</v>
+        <v>17900</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>2.57879656160458</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>2.190907180121209</v>
+        <v>1.729232534027776</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.440986992623174</v>
+        <v>0.3985229729363614</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>0.8072773205574216</v>
+        <v>0.7303133776464583</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>0.4112428551470276</v>
+        <v>0.4362136763476879</v>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -45236,33 +45236,33 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>4420</v>
+        <v>4430</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>-2.428256070640178</v>
+        <v>-2.207505518763797</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.6245503221271895</v>
+        <v>0.5976561705729136</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>-0.0508795718036596</v>
+        <v>-0.0535687346682349</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>3.921265963983961</v>
+        <v>4.347888187658796</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>-0.0148945060923392</v>
+        <v>-0.0320687419588898</v>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -45287,16 +45287,16 @@
         <v>-2.881355932203389</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.5355871946590091</v>
+        <v>0.5540285769783065</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>-0.1399281785281577</v>
+        <v>-0.140322221631417</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>1.201420144640395</v>
+        <v>1.369303324163979</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>0</v>
+        <v>-0.5994527842663226</v>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -45326,33 +45326,33 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>2.389078498293506</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>3.134215301157236</v>
+        <v>2.907277713201065</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.0307826498278561</v>
+        <v>0.0025032741688276</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>1.034956202671817</v>
+        <v>0.9939061925160714</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>0.07977270098399621</v>
+        <v>0</v>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -45371,33 +45371,33 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>7750</v>
+        <v>7810</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>2.108036890645581</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1.766515412592442</v>
+        <v>1.794061189744712</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>-0.009415211521080101</v>
+        <v>-0.009767218856966599</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>1.076159728502105</v>
+        <v>1.185695830206121</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>-0.3463902616707809</v>
+        <v>-0.4363419826010773</v>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -45422,16 +45422,16 @@
         <v>2.979942693409732</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.969180464178577</v>
+        <v>2.190907180121209</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.3507136729969617</v>
+        <v>0.440986992623174</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.8883241394178399</v>
+        <v>0.8072773205574216</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>0.2482293556645952</v>
+        <v>0.4112428551470276</v>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
@@ -45442,12 +45442,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -45461,26 +45461,26 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>16870</v>
+        <v>4420</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>-2.485549132947973</v>
+        <v>-2.428256070640178</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.474544067309485</v>
+        <v>0.6245503221271895</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>-0.4874924073057561</v>
+        <v>-0.0508795718036596</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0.4295222967984636</v>
+        <v>3.921265963983961</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>-0.7309510254835279</v>
+        <v>-0.0148945060923392</v>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -45492,7 +45492,7 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -45506,19 +45506,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>4400</v>
+        <v>5730</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.5893419733212854</v>
+        <v>0.5355871946590091</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>-0.046754876249359</v>
+        <v>-0.1399281785281577</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>3.728310942539573</v>
+        <v>1.201420144640395</v>
       </c>
       <c r="J36" s="11" t="n">
         <v>0</v>
@@ -45532,12 +45532,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -45551,206 +45551,206 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>14200</v>
+        <v>3010</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>2.824040550325857</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.903407620274961</v>
+        <v>3.134215301157236</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.1248884295297009</v>
+        <v>0.0307826498278561</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>2.075257593336716</v>
+        <v>1.034956202671817</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>0.5612226806540116</v>
+        <v>0.07977270098399621</v>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>9050</v>
+        <v>7750</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.108036890645581</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.913020062778806</v>
+        <v>1.766515412592442</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.0090833768467677</v>
+        <v>-0.009415211521080101</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.545715908902803</v>
+        <v>1.076159728502105</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>0</v>
+        <v>-0.3463902616707809</v>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>5730</v>
+        <v>17970</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.5445114161230384</v>
+        <v>1.969180464178577</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>-0.1249625745875403</v>
+        <v>0.3507136729969617</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>1.192261145958613</v>
+        <v>0.8883241394178399</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>0</v>
+        <v>0.2482293556645952</v>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>3000</v>
+        <v>16870</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>2.389078498293506</v>
+        <v>-2.485549132947973</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>3.165329154162865</v>
+        <v>0.474544067309485</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.029665345422545</v>
+        <v>-0.4874924073057561</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.954539358718734</v>
+        <v>0.4295222967984636</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>0.1259711324552865</v>
+        <v>-0.7309510254835279</v>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>7800</v>
+        <v>4400</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>2.766798418972338</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>1.725083403445673</v>
+        <v>0.5893419733212854</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>-0.08579879894624071</v>
+        <v>-0.046754876249359</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>1.056029600360929</v>
+        <v>3.728310942539573</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>-0.6699986693081985</v>
+        <v>0</v>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -45762,7 +45762,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -45776,26 +45776,26 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>17970</v>
+        <v>14200</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>2.824040550325857</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>1.889882520350639</v>
+        <v>1.903407620274961</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.3090822889411254</v>
+        <v>0.1248884295297009</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.8960426470119435</v>
+        <v>2.075257593336716</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>0.2025530832749217</v>
+        <v>0.5612226806540116</v>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
@@ -45807,187 +45807,187 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>4400</v>
+        <v>9050</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.5941788492156362</v>
+        <v>0.913020062778806</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>-0.0388573261204135</v>
+        <v>0.0090833768467677</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>3.975729602752558</v>
+        <v>0.545715908902803</v>
       </c>
       <c r="J43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>14200</v>
+        <v>5730</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>2.824040550325857</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>1.903407620274961</v>
+        <v>0.5445114161230384</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.1248884295297009</v>
+        <v>-0.1249625745875403</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>1.867731834003045</v>
+        <v>1.192261145958613</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>0.656918747801618</v>
+        <v>0</v>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>9050</v>
+        <v>3000</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.389078498293506</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.926884653893478</v>
+        <v>3.165329154162865</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.0401115407233935</v>
+        <v>0.029665345422545</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>0.5395315359600464</v>
+        <v>0.954539358718734</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>0.08094597773752971</v>
+        <v>0.1259711324552865</v>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>5730</v>
+        <v>7800</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.766798418972338</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.5272199912977696</v>
+        <v>1.725083403445673</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>-0.1245528147806835</v>
+        <v>-0.08579879894624071</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>1.076477045272898</v>
+        <v>1.056029600360929</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0</v>
+        <v>-0.6699986693081985</v>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -46001,22 +46001,22 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>3010</v>
+        <v>17970</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>2.974820557468799</v>
+        <v>1.889882520350639</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.0294887646433008</v>
+        <v>0.3090822889411254</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>0.8642282322569601</v>
+        <v>0.8960426470119435</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>0.1407840639948041</v>
+        <v>0.2025530832749217</v>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
@@ -46027,45 +46027,45 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>7810</v>
+        <v>4400</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>2.297789987704775</v>
+        <v>0.5941788492156362</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>-0.013063333107265</v>
+        <v>-0.0388573261204135</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>1.406449867473435</v>
+        <v>3.975729602752558</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>-0.0178174891841188</v>
+        <v>0</v>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -46077,7 +46077,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -46091,26 +46091,26 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>17960</v>
+        <v>14200</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>2.922636103151865</v>
+        <v>2.824040550325857</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>1.55466694445312</v>
+        <v>1.903407620274961</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.2531747102032364</v>
+        <v>0.1248884295297009</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>0.9846156423307446</v>
+        <v>1.867731834003045</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>0</v>
+        <v>0.656918747801618</v>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
@@ -46122,47 +46122,47 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>4400</v>
+        <v>9050</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.6185289371636261</v>
+        <v>0.926884653893478</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>-0.0377731630590493</v>
+        <v>0.0401115407233935</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>3.679412908865234</v>
+        <v>0.5395315359600464</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>0</v>
+        <v>0.08094597773752971</v>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -46187,13 +46187,13 @@
         <v>-2.881355932203389</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.4937400414930954</v>
+        <v>0.5272199912977696</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>-0.1222132407328641</v>
+        <v>-0.1245528147806835</v>
       </c>
       <c r="I51" s="13" t="n">
-        <v>0.9968834147596488</v>
+        <v>1.076477045272898</v>
       </c>
       <c r="J51" s="11" t="n">
         <v>0</v>
@@ -46207,7 +46207,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -46232,27 +46232,27 @@
         <v>2.730375426621157</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>2.805502476481756</v>
+        <v>2.974820557468799</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>0.0286703552889192</v>
+        <v>0.0294887646433008</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>0.8081067673626574</v>
+        <v>0.8642282322569601</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>0</v>
+        <v>0.1407840639948041</v>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -46271,22 +46271,22 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>7790</v>
+        <v>7810</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>2.635046113306982</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>2.414674214115634</v>
+        <v>2.297789987704775</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>0.0127230927019704</v>
+        <v>-0.013063333107265</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>1.422393408083326</v>
+        <v>1.406449867473435</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>0.0398667520708331</v>
+        <v>-0.0178174891841188</v>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -46316,19 +46316,19 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>17970</v>
+        <v>17960</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>2.922636103151865</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>1.607133387836861</v>
+        <v>1.55466694445312</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>0.2464455344870157</v>
+        <v>0.2531747102032364</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>0.91955652781301</v>
+        <v>0.9846156423307446</v>
       </c>
       <c r="J54" s="11" t="n">
         <v>0</v>
@@ -46342,7 +46342,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -46367,13 +46367,13 @@
         <v>-2.86975717439294</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.6380057024485423</v>
+        <v>0.6185289371636261</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>-0.0349953657328336</v>
+        <v>-0.0377731630590493</v>
       </c>
       <c r="I55" s="13" t="n">
-        <v>3.606623965359001</v>
+        <v>3.679412908865234</v>
       </c>
       <c r="J55" s="11" t="n">
         <v>0</v>
@@ -46392,40 +46392,40 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>14200</v>
+        <v>5730</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>2.824040550325857</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>1.824261716975314</v>
+        <v>0.4937400414930954</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>0.1307677581067961</v>
+        <v>-0.1222132407328641</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>1.725060842979444</v>
+        <v>0.9968834147596488</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>0.6322771692411546</v>
+        <v>0</v>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -46437,187 +46437,187 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>9530</v>
+        <v>3010</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>-2.953156822810588</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.5758499398433853</v>
+        <v>2.805502476481756</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>-0.2650766656844744</v>
+        <v>0.0286703552889192</v>
       </c>
       <c r="I57" s="13" t="n">
-        <v>2.432491244322447</v>
+        <v>0.8081067673626574</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>-0.056343488202932</v>
+        <v>0</v>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9050</v>
+        <v>7790</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.635046113306982</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.960611509576484</v>
+        <v>2.414674214115634</v>
       </c>
       <c r="H58" s="11" t="n">
-        <v>0.1260710865210963</v>
+        <v>0.0127230927019704</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>0.5241791150423325</v>
+        <v>1.422393408083326</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>0.5429645795633814</v>
+        <v>0.0398667520708331</v>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>5730</v>
+        <v>17970</v>
       </c>
       <c r="F59" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.6156123383391957</v>
+        <v>1.607133387836861</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>-0.3674118812677964</v>
+        <v>0.2464455344870157</v>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2.392204572137504</v>
+        <v>0.91955652781301</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>-0.5085233046241658</v>
+        <v>0</v>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>3010</v>
+        <v>4400</v>
       </c>
       <c r="F60" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>3.033484385649488</v>
+        <v>0.6380057024485423</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>0.0253710376368312</v>
+        <v>-0.0349953657328336</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>0.837179514381883</v>
+        <v>3.606623965359001</v>
       </c>
       <c r="J60" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -46631,22 +46631,22 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>7770</v>
+        <v>14200</v>
       </c>
       <c r="F61" s="13" t="n">
-        <v>2.371541501976293</v>
+        <v>2.824040550325857</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>2.272648619367283</v>
+        <v>1.824261716975314</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>0.0101379998842666</v>
+        <v>0.1307677581067961</v>
       </c>
       <c r="I61" s="13" t="n">
-        <v>1.312086042009746</v>
+        <v>1.725060842979444</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>0.1565588753405844</v>
+        <v>0.6322771692411546</v>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
@@ -46657,45 +46657,45 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>17970</v>
+        <v>9530</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>-2.953156822810588</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>1.570667684838037</v>
+        <v>0.5758499398433853</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>0.2442827695237164</v>
+        <v>-0.2650766656844744</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>0.8503928303970997</v>
+        <v>2.432491244322447</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>0</v>
+        <v>-0.056343488202932</v>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
@@ -46707,36 +46707,36 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>16790</v>
+        <v>9050</v>
       </c>
       <c r="F63" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.4527661852094354</v>
+        <v>0.960611509576484</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>-0.408888591532126</v>
+        <v>0.1260710865210963</v>
       </c>
       <c r="I63" s="13" t="n">
-        <v>1.148994176087906</v>
+        <v>0.5241791150423325</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>-0.3990572652825598</v>
+        <v>0.5429645795633814</v>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
@@ -46752,40 +46752,40 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>14200</v>
+        <v>5730</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>2.824040550325857</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>1.824261716975314</v>
+        <v>0.6156123383391957</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>0.1307677581067961</v>
+        <v>-0.3674118812677964</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>1.581305772731157</v>
+        <v>2.392204572137504</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>0.4985987812217875</v>
+        <v>-0.5085233046241658</v>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -46797,52 +46797,52 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>9530</v>
+        <v>3010</v>
       </c>
       <c r="F65" s="13" t="n">
-        <v>-2.953156822810588</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.5635909786175041</v>
+        <v>3.033484385649488</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>-0.2564928385075934</v>
+        <v>0.0253710376368312</v>
       </c>
       <c r="I65" s="13" t="n">
-        <v>2.281728840105457</v>
+        <v>0.837179514381883</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>-0.0366473118207462</v>
+        <v>0</v>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -46856,33 +46856,33 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>3010</v>
+        <v>7770</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>2.371541501976293</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>3.163774753829399</v>
+        <v>2.272648619367283</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>0.0250547898455582</v>
+        <v>0.0101379998842666</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>0.7825430184702372</v>
+        <v>1.312086042009746</v>
       </c>
       <c r="J66" s="11" t="n">
-        <v>0</v>
+        <v>0.1565588753405844</v>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -46907,13 +46907,13 @@
         <v>2.979942693409732</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>1.599320200324807</v>
+        <v>1.570667684838037</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>0.2429938374339789</v>
+        <v>0.2442827695237164</v>
       </c>
       <c r="I67" s="13" t="n">
-        <v>0.7891427711496229</v>
+        <v>0.8503928303970997</v>
       </c>
       <c r="J67" s="11" t="n">
         <v>0</v>
@@ -46927,135 +46927,135 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>9050</v>
+        <v>16790</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.949706792858541</v>
+        <v>0.4527661852094354</v>
       </c>
       <c r="H68" s="11" t="n">
-        <v>0.1493062800066627</v>
+        <v>-0.408888591532126</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>0.5143425125689732</v>
+        <v>1.148994176087906</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>0.6058535331332595</v>
+        <v>-0.3990572652825598</v>
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>5730</v>
+        <v>14200</v>
       </c>
       <c r="F69" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.824040550325857</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.5375758857583117</v>
+        <v>1.824261716975314</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>-0.4753009126653406</v>
+        <v>0.1307677581067961</v>
       </c>
       <c r="I69" s="13" t="n">
-        <v>3.032546100073388</v>
+        <v>1.581305772731157</v>
       </c>
       <c r="J69" s="11" t="n">
-        <v>-0.603772690746033</v>
+        <v>0.4985987812217875</v>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>7780</v>
+        <v>9530</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>2.503293807641627</v>
+        <v>-2.953156822810588</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>2.196118552284062</v>
+        <v>0.5635909786175041</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>0.008325820635004</v>
+        <v>-0.2564928385075934</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>1.236773596759691</v>
+        <v>2.281728840105457</v>
       </c>
       <c r="J70" s="11" t="n">
-        <v>0.1579199019969492</v>
+        <v>-0.0366473118207462</v>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -47067,40 +47067,40 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>16790</v>
+        <v>3010</v>
       </c>
       <c r="F71" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.417689321791477</v>
+        <v>3.163774753829399</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>-0.4430809042780307</v>
+        <v>0.0250547898455582</v>
       </c>
       <c r="I71" s="13" t="n">
-        <v>1.148470735953928</v>
+        <v>0.7825430184702372</v>
       </c>
       <c r="J71" s="11" t="n">
-        <v>-0.4544871545260938</v>
+        <v>0</v>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
@@ -47112,40 +47112,40 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>4400</v>
+        <v>17970</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.6319043223496534</v>
+        <v>1.599320200324807</v>
       </c>
       <c r="H72" s="11" t="n">
-        <v>-0.0328067241211781</v>
+        <v>0.2429938374339789</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>3.252864872176527</v>
+        <v>0.7891427711496229</v>
       </c>
       <c r="J72" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
@@ -47157,265 +47157,265 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>9530</v>
+        <v>9050</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>-2.953156822810588</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.5670792635344607</v>
+        <v>0.949706792858541</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>-0.2237487800604898</v>
+        <v>0.1493062800066627</v>
       </c>
       <c r="I73" s="13" t="n">
-        <v>2.18096723996436</v>
+        <v>0.5143425125689732</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>0.169591547811354</v>
+        <v>0.6058535331332595</v>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>9050</v>
+        <v>5730</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>1.031231737599037</v>
+        <v>0.5375758857583117</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>0.2492535672053584</v>
+        <v>-0.4753009126653406</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>0.5412596692241931</v>
+        <v>3.032546100073388</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>0.7698861949177845</v>
+        <v>-0.603772690746033</v>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>5730</v>
+        <v>7780</v>
       </c>
       <c r="F75" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.503293807641627</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.5366270793444252</v>
+        <v>2.196118552284062</v>
       </c>
       <c r="H75" s="11" t="n">
-        <v>-0.4623919475787963</v>
+        <v>0.008325820635004</v>
       </c>
       <c r="I75" s="13" t="n">
-        <v>2.894217168172694</v>
+        <v>1.236773596759691</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>-0.5855437263754167</v>
+        <v>0.1579199019969492</v>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>3010</v>
+        <v>16790</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>2.906050316158045</v>
+        <v>0.417689321791477</v>
       </c>
       <c r="H76" s="11" t="n">
-        <v>0.0228984828475074</v>
+        <v>-0.4430809042780307</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>0.7951273707109837</v>
+        <v>1.148470735953928</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>0</v>
+        <v>-0.4544871545260938</v>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>7810</v>
+        <v>4400</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>2.18736922843021</v>
+        <v>0.6319043223496534</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>0.0066142114803579</v>
+        <v>-0.0328067241211781</v>
       </c>
       <c r="I77" s="13" t="n">
-        <v>1.151445173723772</v>
+        <v>3.252864872176527</v>
       </c>
       <c r="J77" s="11" t="n">
-        <v>-0.195182865225298</v>
+        <v>0</v>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>17970</v>
+        <v>9530</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>-2.953156822810588</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>1.505494732323499</v>
+        <v>0.5670792635344607</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0.238386518200536</v>
+        <v>-0.2237487800604898</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>0.7469438008977356</v>
+        <v>2.18096723996436</v>
       </c>
       <c r="J78" s="11" t="n">
-        <v>0</v>
+        <v>0.169591547811354</v>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -47427,40 +47427,40 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>16790</v>
+        <v>9050</v>
       </c>
       <c r="F79" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.4189373864904488</v>
+        <v>1.031231737599037</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>-0.4409344058053376</v>
+        <v>0.2492535672053584</v>
       </c>
       <c r="I79" s="13" t="n">
-        <v>1.071560094992939</v>
+        <v>0.5412596692241931</v>
       </c>
       <c r="J79" s="11" t="n">
-        <v>-0.4486484465547538</v>
+        <v>0.7698861949177845</v>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
@@ -47472,7 +47472,7 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -47486,22 +47486,22 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>4400</v>
+        <v>5730</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.6365040541020304</v>
+        <v>0.5366270793444252</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>-0.0309886629567394</v>
+        <v>-0.4623919475787963</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>3.195507141727467</v>
+        <v>2.894217168172694</v>
       </c>
       <c r="J80" s="11" t="n">
-        <v>0</v>
+        <v>-0.5855437263754167</v>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
@@ -47517,232 +47517,232 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>9600</v>
+        <v>3010</v>
       </c>
       <c r="F81" s="13" t="n">
-        <v>-2.24032586558045</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.5706998440494752</v>
+        <v>2.906050316158045</v>
       </c>
       <c r="H81" s="11" t="n">
-        <v>-0.3003968851673189</v>
+        <v>0.0228984828475074</v>
       </c>
       <c r="I81" s="13" t="n">
-        <v>2.584929411937674</v>
+        <v>0.7951273707109837</v>
       </c>
       <c r="J81" s="11" t="n">
-        <v>-0.3965050892417165</v>
+        <v>0</v>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>9050</v>
+        <v>7810</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>1.059559622454604</v>
+        <v>2.18736922843021</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>0.2490286456104793</v>
+        <v>0.0066142114803579</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>0.5056321635919191</v>
+        <v>1.151445173723772</v>
       </c>
       <c r="J82" s="11" t="n">
-        <v>0.8468842359281756</v>
+        <v>-0.195182865225298</v>
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>5730</v>
+        <v>17970</v>
       </c>
       <c r="F83" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.5265580464263749</v>
+        <v>1.505494732323499</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>-0.4621619297306893</v>
+        <v>0.238386518200536</v>
       </c>
       <c r="I83" s="13" t="n">
-        <v>2.702604798287127</v>
+        <v>0.7469438008977356</v>
       </c>
       <c r="J83" s="11" t="n">
-        <v>-0.6899393798562677</v>
+        <v>0</v>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>3010</v>
+        <v>16790</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>2.868549683819972</v>
+        <v>0.4189373864904488</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0.0156944369167469</v>
+        <v>-0.4409344058053376</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>1.083008040013274</v>
+        <v>1.071560094992939</v>
       </c>
       <c r="J84" s="11" t="n">
-        <v>0</v>
+        <v>-0.4486484465547538</v>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>7800</v>
+        <v>4400</v>
       </c>
       <c r="F85" s="13" t="n">
-        <v>2.766798418972338</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>2.096692945174147</v>
+        <v>0.6365040541020304</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>0.006491124981343</v>
+        <v>-0.0309886629567394</v>
       </c>
       <c r="I85" s="13" t="n">
-        <v>1.095087989148905</v>
+        <v>3.195507141727467</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>-0.0779043649311072</v>
+        <v>0</v>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -47756,22 +47756,22 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>16790</v>
+        <v>9600</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>-2.24032586558045</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.3961931703583283</v>
+        <v>0.5706998440494752</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>-0.4387263419923682</v>
+        <v>-0.3003968851673189</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>1.0050901658523</v>
+        <v>2.584929411937674</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>-0.7534697280978908</v>
+        <v>-0.3965050892417165</v>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
@@ -47787,40 +47787,40 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>4400</v>
+        <v>9050</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.6505709759876975</v>
+        <v>1.059559622454604</v>
       </c>
       <c r="H87" s="11" t="n">
-        <v>-0.029695433661175</v>
+        <v>0.2490286456104793</v>
       </c>
       <c r="I87" s="13" t="n">
-        <v>3.110856661638215</v>
+        <v>0.5056321635919191</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>0</v>
+        <v>0.8468842359281756</v>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
@@ -47832,7 +47832,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -47846,22 +47846,22 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>9530</v>
+        <v>5730</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>-2.953156822810588</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5864630713509262</v>
+        <v>0.5265580464263749</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>-0.2817208799958648</v>
+        <v>-0.4621619297306893</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>2.63252280092487</v>
+        <v>2.702604798287127</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>-0.3365059203221153</v>
+        <v>-0.6899393798562677</v>
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
@@ -47872,192 +47872,192 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>9050</v>
+        <v>3010</v>
       </c>
       <c r="F89" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>1.080348525748263</v>
+        <v>2.868549683819972</v>
       </c>
       <c r="H89" s="11" t="n">
-        <v>0.2484101770711222</v>
+        <v>0.0156944369167469</v>
       </c>
       <c r="I89" s="13" t="n">
-        <v>0.4752108659090508</v>
+        <v>1.083008040013274</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>0.9714629334430572</v>
+        <v>0</v>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>5730</v>
+        <v>7800</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.766798418972338</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.5215801058198895</v>
+        <v>2.096692945174147</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>-0.4621093379190268</v>
+        <v>0.006491124981343</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>2.533978428195138</v>
+        <v>1.095087989148905</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>0</v>
+        <v>-0.0779043649311072</v>
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>3010</v>
+        <v>16790</v>
       </c>
       <c r="F91" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>2.842469225591382</v>
+        <v>0.3961931703583283</v>
       </c>
       <c r="H91" s="11" t="n">
-        <v>0.0148684266604927</v>
+        <v>-0.4387263419923682</v>
       </c>
       <c r="I91" s="13" t="n">
-        <v>1.071753300345312</v>
+        <v>1.0050901658523</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>0</v>
+        <v>-0.7534697280978908</v>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>7810</v>
+        <v>4400</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>1.995257281648193</v>
+        <v>0.6505709759876975</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>0.0063288504411584</v>
+        <v>-0.029695433661175</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>1.053002070385929</v>
+        <v>3.110856661638215</v>
       </c>
       <c r="J92" s="11" t="n">
-        <v>-0.0354251405186619</v>
+        <v>0</v>
       </c>
       <c r="K92" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -48071,22 +48071,22 @@
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>16790</v>
+        <v>9530</v>
       </c>
       <c r="F93" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>-2.953156822810588</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.4080281169423219</v>
+        <v>0.5864630713509262</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>-0.4106260533055349</v>
+        <v>-0.2817208799958648</v>
       </c>
       <c r="I93" s="13" t="n">
-        <v>1.02661685878216</v>
+        <v>2.63252280092487</v>
       </c>
       <c r="J93" s="11" t="n">
-        <v>-0.09094645932310461</v>
+        <v>-0.3365059203221153</v>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
@@ -48102,40 +48102,40 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4400</v>
+        <v>9050</v>
       </c>
       <c r="F94" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.6468927762585351</v>
+        <v>1.080348525748263</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>-0.0269069376053889</v>
+        <v>0.2484101770711222</v>
       </c>
       <c r="I94" s="13" t="n">
-        <v>3.215237003935048</v>
+        <v>0.4752108659090508</v>
       </c>
       <c r="J94" s="11" t="n">
-        <v>0</v>
+        <v>0.9714629334430572</v>
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
@@ -48147,7 +48147,7 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
@@ -48161,22 +48161,22 @@
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>9610</v>
+        <v>5730</v>
       </c>
       <c r="F95" s="13" t="n">
-        <v>-2.138492871690423</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.5956704924976068</v>
+        <v>0.5215801058198895</v>
       </c>
       <c r="H95" s="11" t="n">
-        <v>-0.2824991935885951</v>
+        <v>-0.4621093379190268</v>
       </c>
       <c r="I95" s="13" t="n">
-        <v>2.512038800044566</v>
+        <v>2.533978428195138</v>
       </c>
       <c r="J95" s="11" t="n">
-        <v>-0.4177983548469787</v>
+        <v>0</v>
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
@@ -48187,192 +48187,192 @@
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>9050</v>
+        <v>3010</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>1.084915481269507</v>
+        <v>2.842469225591382</v>
       </c>
       <c r="H96" s="11" t="n">
-        <v>0.2458566291040221</v>
+        <v>0.0148684266604927</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>0.4519046745983295</v>
+        <v>1.071753300345312</v>
       </c>
       <c r="J96" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>5730</v>
+        <v>7810</v>
       </c>
       <c r="F97" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.5075521299626168</v>
+        <v>1.995257281648193</v>
       </c>
       <c r="H97" s="11" t="n">
-        <v>-0.4617148831867242</v>
+        <v>0.0063288504411584</v>
       </c>
       <c r="I97" s="13" t="n">
-        <v>2.386944771475565</v>
+        <v>1.053002070385929</v>
       </c>
       <c r="J97" s="11" t="n">
-        <v>0</v>
+        <v>-0.0354251405186619</v>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3010</v>
+        <v>16790</v>
       </c>
       <c r="F98" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>2.954892615848901</v>
+        <v>0.4080281169423219</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.0148166144864156</v>
+        <v>-0.4106260533055349</v>
       </c>
       <c r="I98" s="13" t="n">
-        <v>1.012237969851032</v>
+        <v>1.02661685878216</v>
       </c>
       <c r="J98" s="11" t="n">
-        <v>0</v>
+        <v>-0.09094645932310461</v>
       </c>
       <c r="K98" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>7800</v>
+        <v>4400</v>
       </c>
       <c r="F99" s="13" t="n">
-        <v>2.766798418972338</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>1.906299790031626</v>
+        <v>0.6468927762585351</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0.0061979413870712</v>
+        <v>-0.0269069376053889</v>
       </c>
       <c r="I99" s="13" t="n">
-        <v>1.012001351568304</v>
+        <v>3.215237003935048</v>
       </c>
       <c r="J99" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -48386,22 +48386,22 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>16790</v>
+        <v>9610</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>-2.138492871690423</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.4080281169423219</v>
+        <v>0.5956704924976068</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>-0.4106260533055349</v>
+        <v>-0.2824991935885951</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>0.9662276317949744</v>
+        <v>2.512038800044566</v>
       </c>
       <c r="J100" s="11" t="n">
-        <v>-0.0955270142524723</v>
+        <v>-0.4177983548469787</v>
       </c>
       <c r="K100" s="10" t="inlineStr">
         <is>
@@ -48417,40 +48417,40 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>4400</v>
+        <v>9050</v>
       </c>
       <c r="F101" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.6380228210831678</v>
+        <v>1.084915481269507</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>-0.026845462097238</v>
+        <v>0.2458566291040221</v>
       </c>
       <c r="I101" s="13" t="n">
-        <v>3.032963660569393</v>
+        <v>0.4519046745983295</v>
       </c>
       <c r="J101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
@@ -48462,52 +48462,52 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>14160</v>
+        <v>5730</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>2.534395365677056</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>1.774975578539237</v>
+        <v>0.5075521299626168</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0.1292741298058244</v>
+        <v>-0.4617148831867242</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>1.661690910646654</v>
+        <v>2.386944771475565</v>
       </c>
       <c r="J102" s="11" t="n">
-        <v>0.0423420700229829</v>
+        <v>0</v>
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
@@ -48521,83 +48521,83 @@
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>14180</v>
+        <v>3010</v>
       </c>
       <c r="F103" s="13" t="n">
-        <v>2.679217958001456</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>1.867288457081341</v>
+        <v>2.954892615848901</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0.1418771870084743</v>
+        <v>0.0148166144864156</v>
       </c>
       <c r="I103" s="13" t="n">
-        <v>1.635231413314682</v>
+        <v>1.012237969851032</v>
       </c>
       <c r="J103" s="11" t="n">
-        <v>0.0923884833894585</v>
+        <v>0</v>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>9050</v>
+        <v>7800</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.766798418972338</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>1.093094326636024</v>
+        <v>1.906299790031626</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0.2457484546245272</v>
+        <v>0.0061979413870712</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>0.4269868104240233</v>
+        <v>1.012001351568304</v>
       </c>
       <c r="J104" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
@@ -48611,22 +48611,22 @@
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>5730</v>
+        <v>16790</v>
       </c>
       <c r="F105" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.506595071611127</v>
+        <v>0.4080281169423219</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>-0.4560402162412974</v>
+        <v>-0.4106260533055349</v>
       </c>
       <c r="I105" s="13" t="n">
-        <v>2.282201136569762</v>
+        <v>0.9662276317949744</v>
       </c>
       <c r="J105" s="11" t="n">
-        <v>0</v>
+        <v>-0.0955270142524723</v>
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
@@ -48637,57 +48637,57 @@
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>3010</v>
+        <v>4400</v>
       </c>
       <c r="F106" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>3.011282237622363</v>
+        <v>0.6380228210831678</v>
       </c>
       <c r="H106" s="11" t="n">
-        <v>0.0148161372581679</v>
+        <v>-0.026845462097238</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>0.9560333341320408</v>
+        <v>3.032963660569393</v>
       </c>
       <c r="J106" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
@@ -48701,26 +48701,26 @@
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>7790</v>
+        <v>14160</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>2.635046113306982</v>
+        <v>2.534395365677056</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>1.884656141710202</v>
+        <v>1.774975578539237</v>
       </c>
       <c r="H107" s="11" t="n">
-        <v>0.0061527464653133</v>
+        <v>0.1292741298058244</v>
       </c>
       <c r="I107" s="13" t="n">
-        <v>0.9627982403499812</v>
+        <v>1.661690910646654</v>
       </c>
       <c r="J107" s="11" t="n">
-        <v>0</v>
+        <v>0.0423420700229829</v>
       </c>
       <c r="K107" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
@@ -48732,40 +48732,40 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>16790</v>
+        <v>14180</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.679217958001456</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.4298984741889132</v>
+        <v>1.867288457081341</v>
       </c>
       <c r="H108" s="11" t="n">
-        <v>-0.3669627855114713</v>
+        <v>0.1418771870084743</v>
       </c>
       <c r="I108" s="13" t="n">
-        <v>1.509727021016529</v>
+        <v>1.635231413314682</v>
       </c>
       <c r="J108" s="11" t="n">
-        <v>-0.2787060806527796</v>
+        <v>0.0923884833894585</v>
       </c>
       <c r="K108" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
@@ -48777,47 +48777,47 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>4400</v>
+        <v>9050</v>
       </c>
       <c r="F109" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.6328091866759772</v>
+        <v>1.093094326636024</v>
       </c>
       <c r="H109" s="11" t="n">
-        <v>-0.026820829007248</v>
+        <v>0.2457484546245272</v>
       </c>
       <c r="I109" s="13" t="n">
-        <v>2.867069423285652</v>
+        <v>0.4269868104240233</v>
       </c>
       <c r="J109" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -48842,13 +48842,13 @@
         <v>-2.881355932203389</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.4983122998011758</v>
+        <v>0.506595071611127</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>-0.4554674806666449</v>
+        <v>-0.4560402162412974</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>2.164786128200908</v>
+        <v>2.282201136569762</v>
       </c>
       <c r="J110" s="11" t="n">
         <v>0</v>
@@ -48862,180 +48862,180 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>16790</v>
+        <v>3010</v>
       </c>
       <c r="F111" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.3961998314620105</v>
+        <v>3.011282237622363</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>-0.3896380974774431</v>
+        <v>0.0148161372581679</v>
       </c>
       <c r="I111" s="13" t="n">
-        <v>1.534365902874917</v>
+        <v>0.9560333341320408</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>-0.3628754399610071</v>
+        <v>0</v>
       </c>
       <c r="K111" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>9050</v>
+        <v>7790</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.635046113306982</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>1.120631989981804</v>
+        <v>1.884656141710202</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0.2452966822187575</v>
+        <v>0.0061527464653133</v>
       </c>
       <c r="I112" s="13" t="n">
-        <v>0.4052591508571492</v>
+        <v>0.9627982403499812</v>
       </c>
       <c r="J112" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>3010</v>
+        <v>16790</v>
       </c>
       <c r="F113" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>3.067600174625121</v>
+        <v>0.4298984741889132</v>
       </c>
       <c r="H113" s="11" t="n">
-        <v>0.0147926554373873</v>
+        <v>-0.3669627855114713</v>
       </c>
       <c r="I113" s="13" t="n">
-        <v>0.9071541830002874</v>
+        <v>1.509727021016529</v>
       </c>
       <c r="J113" s="11" t="n">
-        <v>0</v>
+        <v>-0.2787060806527796</v>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>7810</v>
+        <v>4400</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>1.954871194390093</v>
+        <v>0.6328091866759772</v>
       </c>
       <c r="H114" s="11" t="n">
-        <v>0.0041966499129067</v>
+        <v>-0.026820829007248</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>0.9294120571738445</v>
+        <v>2.867069423285652</v>
       </c>
       <c r="J114" s="11" t="n">
-        <v>-0.0401347842356116</v>
+        <v>0</v>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -49047,40 +49047,40 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>17970</v>
+        <v>5730</v>
       </c>
       <c r="F115" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>1.502865117365449</v>
+        <v>0.4983122998011758</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>0.2298953138426504</v>
+        <v>-0.4554674806666449</v>
       </c>
       <c r="I115" s="13" t="n">
-        <v>0.5707161461823183</v>
+        <v>2.164786128200908</v>
       </c>
       <c r="J115" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -49092,7 +49092,7 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
@@ -49106,22 +49106,22 @@
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>4400</v>
+        <v>16790</v>
       </c>
       <c r="F116" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.6194623597749654</v>
+        <v>0.3961998314620105</v>
       </c>
       <c r="H116" s="11" t="n">
-        <v>-0.0265019263303843</v>
+        <v>-0.3896380974774431</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>2.748519214420701</v>
+        <v>1.534365902874917</v>
       </c>
       <c r="J116" s="11" t="n">
-        <v>0</v>
+        <v>-0.3628754399610071</v>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
@@ -49137,40 +49137,40 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
-        <v>14160</v>
+        <v>9050</v>
       </c>
       <c r="F117" s="13" t="n">
-        <v>2.534395365677056</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>1.789879975306671</v>
+        <v>1.120631989981804</v>
       </c>
       <c r="H117" s="11" t="n">
-        <v>0.1199276853152095</v>
+        <v>0.2452966822187575</v>
       </c>
       <c r="I117" s="13" t="n">
-        <v>1.835027186399669</v>
+        <v>0.4052591508571492</v>
       </c>
       <c r="J117" s="11" t="n">
-        <v>0.0590894412736557</v>
+        <v>0</v>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
@@ -49182,187 +49182,187 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>9580</v>
+        <v>3010</v>
       </c>
       <c r="F118" s="13" t="n">
-        <v>-2.443991853360494</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.6229858769382305</v>
+        <v>3.067600174625121</v>
       </c>
       <c r="H118" s="11" t="n">
-        <v>-0.2656359640310742</v>
+        <v>0.0147926554373873</v>
       </c>
       <c r="I118" s="13" t="n">
-        <v>2.190770072358559</v>
+        <v>0.9071541830002874</v>
       </c>
       <c r="J118" s="11" t="n">
-        <v>0.1990833276467314</v>
+        <v>0</v>
       </c>
       <c r="K118" s="10" t="inlineStr">
         <is>
-          <t>منتظر پایداری</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
-        <v>16790</v>
+        <v>7810</v>
       </c>
       <c r="F119" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.3961998314620105</v>
+        <v>1.954871194390093</v>
       </c>
       <c r="H119" s="11" t="n">
-        <v>-0.3896380974774431</v>
+        <v>0.0041966499129067</v>
       </c>
       <c r="I119" s="13" t="n">
-        <v>1.457647607731171</v>
+        <v>0.9294120571738445</v>
       </c>
       <c r="J119" s="11" t="n">
-        <v>-0.3628754399610071</v>
+        <v>-0.0401347842356116</v>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>5730</v>
+        <v>17970</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.4911733112620962</v>
+        <v>1.502865117365449</v>
       </c>
       <c r="H120" s="11" t="n">
-        <v>-0.4518372461435739</v>
+        <v>0.2298953138426504</v>
       </c>
       <c r="I120" s="13" t="n">
-        <v>2.072961192925345</v>
+        <v>0.5707161461823183</v>
       </c>
       <c r="J120" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>9050</v>
+        <v>4400</v>
       </c>
       <c r="F121" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>1.127285384301096</v>
+        <v>0.6194623597749654</v>
       </c>
       <c r="H121" s="11" t="n">
-        <v>0.245032498744864</v>
+        <v>-0.0265019263303843</v>
       </c>
       <c r="I121" s="13" t="n">
-        <v>0.3854114585023766</v>
+        <v>2.748519214420701</v>
       </c>
       <c r="J121" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
@@ -49376,71 +49376,71 @@
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3010</v>
+        <v>14160</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>2.534395365677056</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>2.949165390946744</v>
+        <v>1.789879975306671</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>0.0145517070960089</v>
+        <v>0.1199276853152095</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>0.8760727295182777</v>
+        <v>1.835027186399669</v>
       </c>
       <c r="J122" s="11" t="n">
-        <v>0</v>
+        <v>0.0590894412736557</v>
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید خرید</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
-        <v>7810</v>
+        <v>9580</v>
       </c>
       <c r="F123" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>-2.443991853360494</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>1.939544986924256</v>
+        <v>0.6229858769382305</v>
       </c>
       <c r="H123" s="11" t="n">
-        <v>-0.0026017894160602</v>
+        <v>-0.2656359640310742</v>
       </c>
       <c r="I123" s="13" t="n">
-        <v>0.8939018172803108</v>
+        <v>2.190770072358559</v>
       </c>
       <c r="J123" s="11" t="n">
-        <v>-0.2274151201490933</v>
+        <v>0.1990833276467314</v>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>منتظر پایداری</t>
         </is>
       </c>
     </row>
@@ -49452,40 +49452,40 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>وارس</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>17970</v>
+        <v>16790</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>-2.947976878612713</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>1.539314170519759</v>
+        <v>0.3961998314620105</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>0.2234657041493188</v>
+        <v>-0.3896380974774431</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>0.5577862885700158</v>
+        <v>1.457647607731171</v>
       </c>
       <c r="J124" s="11" t="n">
-        <v>0</v>
+        <v>-0.3628754399610071</v>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -49497,7 +49497,7 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -49511,19 +49511,19 @@
         </is>
       </c>
       <c r="E125" s="12" t="n">
-        <v>4400</v>
+        <v>5730</v>
       </c>
       <c r="F125" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.6036015303861026</v>
+        <v>0.4911733112620962</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>-0.026088190011619</v>
+        <v>-0.4518372461435739</v>
       </c>
       <c r="I125" s="13" t="n">
-        <v>2.652082243089511</v>
+        <v>2.072961192925345</v>
       </c>
       <c r="J125" s="11" t="n">
         <v>0</v>
@@ -49542,40 +49542,40 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>پاکشو</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>14160</v>
+        <v>9050</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>2.534395365677056</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>1.746232488109314</v>
+        <v>1.127285384301096</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>0.1204525427894985</v>
+        <v>0.245032498744864</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>1.744315782087094</v>
+        <v>0.3854114585023766</v>
       </c>
       <c r="J126" s="11" t="n">
-        <v>0.0829339357904447</v>
+        <v>0</v>
       </c>
       <c r="K126" s="10" t="inlineStr">
         <is>
-          <t>تأیید خرید</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
@@ -49587,187 +49587,187 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>شفن</t>
+          <t>شفام</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
-        <v>9530</v>
+        <v>3010</v>
       </c>
       <c r="F127" s="13" t="n">
-        <v>-2.953156822810588</v>
+        <v>2.730375426621157</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.6188757936671109</v>
+        <v>2.949165390946744</v>
       </c>
       <c r="H127" s="11" t="n">
-        <v>-0.2513129021298832</v>
+        <v>0.0145517070960089</v>
       </c>
       <c r="I127" s="13" t="n">
-        <v>2.240612777784579</v>
+        <v>0.8760727295182777</v>
       </c>
       <c r="J127" s="11" t="n">
-        <v>0.0043790367644167</v>
+        <v>0</v>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>فرآور</t>
+          <t>غگل</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>صف-واچ‌لیست</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>9050</v>
+        <v>7810</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>2.957906712172931</v>
+        <v>2.898550724637672</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>1.130305749286305</v>
+        <v>1.939544986924256</v>
       </c>
       <c r="H128" s="11" t="n">
-        <v>0.242343959354237</v>
+        <v>-0.0026017894160602</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>0.3711323952704252</v>
+        <v>0.8939018172803108</v>
       </c>
       <c r="J128" s="11" t="n">
-        <v>0</v>
+        <v>-0.2274151201490933</v>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>رد: ارزش کم</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>ناما</t>
+          <t>دامین</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>انباشت→صف-خرید</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید؟</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
-        <v>5730</v>
+        <v>17970</v>
       </c>
       <c r="F129" s="13" t="n">
-        <v>-2.881355932203389</v>
+        <v>2.979942693409732</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.4832307524098043</v>
+        <v>1.539314170519759</v>
       </c>
       <c r="H129" s="11" t="n">
-        <v>-0.4513536477907807</v>
+        <v>0.2234657041493188</v>
       </c>
       <c r="I129" s="13" t="n">
-        <v>1.976350236313611</v>
+        <v>0.5577862885700158</v>
       </c>
       <c r="J129" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>شفام</t>
+          <t>فروس</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>3010</v>
+        <v>4400</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>2.730375426621157</v>
+        <v>-2.86975717439294</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>2.933459192634188</v>
+        <v>0.6036015303861026</v>
       </c>
       <c r="H130" s="11" t="n">
-        <v>0.0144437269929259</v>
+        <v>-0.026088190011619</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>0.8405953698137613</v>
+        <v>2.652082243089511</v>
       </c>
       <c r="J130" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>غگل</t>
+          <t>پاکشو</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -49781,22 +49781,22 @@
         </is>
       </c>
       <c r="E131" s="12" t="n">
-        <v>7810</v>
+        <v>14160</v>
       </c>
       <c r="F131" s="13" t="n">
-        <v>2.898550724637672</v>
+        <v>2.534395365677056</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>1.921016921119208</v>
+        <v>1.746232488109314</v>
       </c>
       <c r="H131" s="11" t="n">
-        <v>0.0100905486031219</v>
+        <v>0.1204525427894985</v>
       </c>
       <c r="I131" s="13" t="n">
-        <v>0.864603282234411</v>
+        <v>1.744315782087094</v>
       </c>
       <c r="J131" s="11" t="n">
-        <v>0.09277987047930079</v>
+        <v>0.0829339357904447</v>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
@@ -49807,45 +49807,45 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>دامین</t>
+          <t>شفن</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>انباشت→صف-خرید</t>
+          <t>توزیع→صف-فروش</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>خرید؟</t>
+          <t>فروش؟</t>
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>17970</v>
+        <v>9530</v>
       </c>
       <c r="F132" s="13" t="n">
-        <v>2.979942693409732</v>
+        <v>-2.953156822810588</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>1.570423942150205</v>
+        <v>0.6188757936671109</v>
       </c>
       <c r="H132" s="11" t="n">
-        <v>0.2228674367748149</v>
+        <v>-0.2513129021298832</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>0.5326516133925525</v>
+        <v>2.240612777784579</v>
       </c>
       <c r="J132" s="11" t="n">
-        <v>0</v>
+        <v>0.0043790367644167</v>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+          <t>تأیید فروش (روز بعد)</t>
         </is>
       </c>
     </row>
@@ -49857,40 +49857,40 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>وارس</t>
+          <t>فرآور</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>توزیع→صف-فروش</t>
+          <t>صف-واچ‌لیست</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>فروش؟</t>
+          <t>خرید</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
-        <v>16790</v>
+        <v>9050</v>
       </c>
       <c r="F133" s="13" t="n">
-        <v>-2.947976878612713</v>
+        <v>2.957906712172931</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.3067497128333861</v>
+        <v>1.130305749286305</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>-0.4914412655657019</v>
+        <v>0.242343959354237</v>
       </c>
       <c r="I133" s="13" t="n">
-        <v>1.72971038840565</v>
+        <v>0.3711323952704252</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>-0.8585033960670491</v>
+        <v>0</v>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>تأیید فروش (روز بعد)</t>
+          <t>رد: ارزش کم</t>
         </is>
       </c>
     </row>
@@ -49902,7 +49902,7 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>فروس</t>
+          <t>ناما</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
@@ -49916,19 +49916,19 @@
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>4400</v>
+        <v>5730</v>
       </c>
       <c r="F134" s="13" t="n">
-        <v>-2.86975717439294</v>
+        <v>-2.881355932203389</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.5883292519136691</v>
+        <v>0.4832307524098043</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>-0.0260096634251381</v>
+        <v>-0.4513536477907807</v>
       </c>
       <c r="I134" s="13" t="n">
-        <v>2.533342034336921</v>
+        <v>1.976350236313611</v>
       </c>
       <c r="J134" s="11" t="n">
         <v>0</v>
@@ -49947,45 +49947,270 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
+          <t>شفام</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>انباشت→صف-خرید</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>خرید؟</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>2.730375426621157</v>
+      </c>
+      <c r="G135" s="13" t="n">
+        <v>2.933459192634188</v>
+      </c>
+      <c r="H135" s="11" t="n">
+        <v>0.0144437269929259</v>
+      </c>
+      <c r="I135" s="13" t="n">
+        <v>0.8405953698137613</v>
+      </c>
+      <c r="J135" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="10" t="inlineStr">
+        <is>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>غگل</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>انباشت→صف-خرید</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>خرید؟</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="n">
+        <v>7810</v>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>2.898550724637672</v>
+      </c>
+      <c r="G136" s="13" t="n">
+        <v>1.921016921119208</v>
+      </c>
+      <c r="H136" s="11" t="n">
+        <v>0.0100905486031219</v>
+      </c>
+      <c r="I136" s="13" t="n">
+        <v>0.864603282234411</v>
+      </c>
+      <c r="J136" s="11" t="n">
+        <v>0.09277987047930079</v>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>تأیید خرید</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>دامین</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>انباشت→صف-خرید</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>خرید؟</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>17970</v>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>2.979942693409732</v>
+      </c>
+      <c r="G137" s="13" t="n">
+        <v>1.570423942150205</v>
+      </c>
+      <c r="H137" s="11" t="n">
+        <v>0.2228674367748149</v>
+      </c>
+      <c r="I137" s="13" t="n">
+        <v>0.5326516133925525</v>
+      </c>
+      <c r="J137" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>وارس</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>توزیع→صف-فروش</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>فروش؟</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>16790</v>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>-2.947976878612713</v>
+      </c>
+      <c r="G138" s="13" t="n">
+        <v>0.3067497128333861</v>
+      </c>
+      <c r="H138" s="11" t="n">
+        <v>-0.4914412655657019</v>
+      </c>
+      <c r="I138" s="13" t="n">
+        <v>1.72971038840565</v>
+      </c>
+      <c r="J138" s="11" t="n">
+        <v>-0.8585033960670491</v>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
+        <is>
+          <t>تأیید فروش (روز بعد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>فروس</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>توزیع→صف-فروش</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>فروش؟</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>-2.86975717439294</v>
+      </c>
+      <c r="G139" s="13" t="n">
+        <v>0.5883292519136691</v>
+      </c>
+      <c r="H139" s="11" t="n">
+        <v>-0.0260096634251381</v>
+      </c>
+      <c r="I139" s="13" t="n">
+        <v>2.533342034336921</v>
+      </c>
+      <c r="J139" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>تأیید فروش (روز بعد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
           <t>پاکشو</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>انباشت→صف-خرید</t>
         </is>
       </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>خرید؟</t>
         </is>
       </c>
-      <c r="E135" s="12" t="n">
+      <c r="E140" s="12" t="n">
         <v>14220</v>
       </c>
-      <c r="F135" s="13" t="n">
+      <c r="F140" s="13" t="n">
         <v>2.968863142650258</v>
       </c>
-      <c r="G135" s="13" t="n">
+      <c r="G140" s="13" t="n">
         <v>1.641814500239655</v>
       </c>
-      <c r="H135" s="11" t="n">
+      <c r="H140" s="11" t="n">
         <v>0.1135396037565336</v>
       </c>
-      <c r="I135" s="13" t="n">
+      <c r="I140" s="13" t="n">
         <v>1.780270433243316</v>
       </c>
-      <c r="J135" s="11" t="n">
+      <c r="J140" s="11" t="n">
         <v>0.0085910985724231</v>
       </c>
-      <c r="K135" s="10" t="inlineStr">
+      <c r="K140" s="10" t="inlineStr">
         <is>
           <t>رد: جریان ۳۰دقیقه خرید را تأیید نمی‌کند</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K135"/>
+  <autoFilter ref="A1:K140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49996,7 +50221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -54544,7 +54769,7 @@
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
@@ -54558,7 +54783,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -54646,7 +54871,7 @@
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
@@ -54660,7 +54885,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -54867,8 +55092,42 @@
         <v>2</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>صندوق-اهرمی</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>منتظر پایداری</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="11" t="n"/>
+      <c r="F116" s="11" t="n"/>
+      <c r="G116" s="11" t="n"/>
+      <c r="H116" s="11" t="n"/>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L115"/>
+  <autoFilter ref="A1:L116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
